--- a/MVAR_ATSBS_T2W/mvar_p50_atsbs_t2w_ALL.xlsx
+++ b/MVAR_ATSBS_T2W/mvar_p50_atsbs_t2w_ALL.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10608"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10727"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/philliao/Downloads/Code/IB-Math-IA/MVAR_ATSBS_T2W/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3073997C-9E5E-6143-8F82-C80F5544E610}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0265273A-FD27-B64B-B145-C94967639005}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="25600" windowHeight="14320" activeTab="1" xr2:uid="{8F259DD8-93C5-2C49-A1A9-8FF4AA32EA25}"/>
+    <workbookView xWindow="3840" yWindow="660" windowWidth="21760" windowHeight="14320" xr2:uid="{8F259DD8-93C5-2C49-A1A9-8FF4AA32EA25}"/>
   </bookViews>
   <sheets>
     <sheet name="Regression" sheetId="1" r:id="rId1"/>
@@ -301,7 +301,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -324,15 +324,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="centerContinuous"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
@@ -704,33 +696,33 @@
       <c r="F1" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="H1" s="16"/>
-      <c r="I1" s="16" t="s">
+      <c r="H1" s="8"/>
+      <c r="I1" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="J1" s="16" t="s">
+      <c r="J1" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="K1" s="16" t="s">
+      <c r="K1" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="L1" s="16" t="s">
+      <c r="L1" s="8" t="s">
         <v>33</v>
       </c>
       <c r="S1" t="s">
         <v>30</v>
       </c>
-      <c r="Z1" s="16"/>
-      <c r="AA1" s="16" t="s">
+      <c r="Z1" s="8"/>
+      <c r="AA1" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="AB1" s="16" t="s">
+      <c r="AB1" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="AC1" s="16" t="s">
+      <c r="AC1" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="AD1" s="16" t="s">
+      <c r="AD1" s="8" t="s">
         <v>4</v>
       </c>
       <c r="AK1" t="s">
@@ -756,13 +748,9 @@
       <c r="F2">
         <v>2.1459362347382922</v>
       </c>
-      <c r="H2" s="14" t="s">
+      <c r="H2" t="s">
         <v>2</v>
       </c>
-      <c r="I2" s="14"/>
-      <c r="J2" s="14"/>
-      <c r="K2" s="14"/>
-      <c r="L2" s="14"/>
       <c r="S2" s="10" t="s">
         <v>0</v>
       </c>
@@ -781,13 +769,9 @@
       <c r="X2" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="Z2" s="14" t="s">
+      <c r="Z2" t="s">
         <v>2</v>
       </c>
-      <c r="AA2" s="14"/>
-      <c r="AB2" s="14"/>
-      <c r="AC2" s="14"/>
-      <c r="AD2" s="14"/>
       <c r="AK2" s="1" t="s">
         <v>0</v>
       </c>
@@ -839,15 +823,12 @@
       <c r="F3">
         <v>0.74672118366569062</v>
       </c>
-      <c r="H3" s="14" t="s">
+      <c r="H3" t="s">
         <v>4</v>
       </c>
-      <c r="I3" s="14">
+      <c r="I3">
         <v>-3.0981694887970649E-2</v>
       </c>
-      <c r="J3" s="14"/>
-      <c r="K3" s="14"/>
-      <c r="L3" s="14"/>
       <c r="S3" s="1">
         <v>3</v>
       </c>
@@ -866,15 +847,12 @@
       <c r="X3">
         <v>2.2664834554790598</v>
       </c>
-      <c r="Z3" s="14" t="s">
+      <c r="Z3" t="s">
         <v>32</v>
       </c>
-      <c r="AA3" s="14">
+      <c r="AA3">
         <v>-6.8836728522793655E-3</v>
       </c>
-      <c r="AB3" s="14"/>
-      <c r="AC3" s="14"/>
-      <c r="AD3" s="14"/>
       <c r="AK3" s="1">
         <v>1</v>
       </c>
@@ -916,17 +894,15 @@
       <c r="F4">
         <v>2.2664834554790598</v>
       </c>
-      <c r="H4" s="14" t="s">
+      <c r="H4" t="s">
         <v>32</v>
       </c>
-      <c r="I4" s="17">
+      <c r="I4" s="14">
         <v>0.99340559646982052</v>
       </c>
-      <c r="J4" s="14">
+      <c r="J4">
         <v>-7.7544148358323114E-2</v>
       </c>
-      <c r="K4" s="14"/>
-      <c r="L4" s="14"/>
       <c r="S4" s="1">
         <v>7</v>
       </c>
@@ -945,17 +921,15 @@
       <c r="X4">
         <v>4.7154689369407654</v>
       </c>
-      <c r="Z4" s="14" t="s">
+      <c r="Z4" t="s">
         <v>33</v>
       </c>
-      <c r="AA4" s="17">
+      <c r="AA4" s="14">
         <v>0.99248349383008749</v>
       </c>
-      <c r="AB4" s="14">
+      <c r="AB4">
         <v>-5.3990932718608407E-2</v>
       </c>
-      <c r="AC4" s="14"/>
-      <c r="AD4" s="14"/>
       <c r="AK4" s="1">
         <v>2</v>
       </c>
@@ -1000,19 +974,19 @@
       <c r="F5">
         <v>3.1496982489142602</v>
       </c>
-      <c r="H5" s="15" t="s">
+      <c r="H5" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="I5" s="15">
+      <c r="I5" s="7">
         <v>0.4460952341063924</v>
       </c>
-      <c r="J5" s="15">
+      <c r="J5" s="7">
         <v>0.19786407311633453</v>
       </c>
-      <c r="K5" s="15">
+      <c r="K5" s="7">
         <v>0.4131651875236893</v>
       </c>
-      <c r="L5" s="15"/>
+      <c r="L5" s="7"/>
       <c r="S5" s="1">
         <v>8</v>
       </c>
@@ -1031,19 +1005,19 @@
       <c r="X5">
         <v>1.595407111680623</v>
       </c>
-      <c r="Z5" s="15" t="s">
+      <c r="Z5" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="AA5" s="15">
+      <c r="AA5" s="7">
         <v>0.10698893436704154</v>
       </c>
-      <c r="AB5" s="15">
+      <c r="AB5" s="7">
         <v>1.4137457492225548E-2</v>
       </c>
-      <c r="AC5" s="15">
+      <c r="AC5" s="7">
         <v>4.2642549234900885E-2</v>
       </c>
-      <c r="AD5" s="15"/>
+      <c r="AD5" s="7"/>
       <c r="AK5" s="1">
         <v>5</v>
       </c>
@@ -1109,11 +1083,11 @@
       <c r="X6">
         <v>3.1974629705323179</v>
       </c>
-      <c r="Z6" s="19"/>
-      <c r="AA6" s="19"/>
-      <c r="AB6" s="19"/>
-      <c r="AC6" s="19"/>
-      <c r="AD6" s="19"/>
+      <c r="Z6" s="15"/>
+      <c r="AA6" s="15"/>
+      <c r="AB6" s="15"/>
+      <c r="AC6" s="15"/>
+      <c r="AD6" s="15"/>
       <c r="AK6" s="1">
         <v>10</v>
       </c>
@@ -1256,22 +1230,22 @@
       <c r="F10">
         <v>2.4929636228042602</v>
       </c>
-      <c r="H10" s="18" t="s">
+      <c r="H10" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="I10" s="18"/>
+      <c r="I10" s="9"/>
     </row>
     <row r="11" spans="1:48" x14ac:dyDescent="0.2">
-      <c r="H11" s="14" t="s">
+      <c r="H11" t="s">
         <v>8</v>
       </c>
-      <c r="I11" s="14">
+      <c r="I11">
         <v>0.88738723805876785</v>
       </c>
-      <c r="Z11" s="18" t="s">
+      <c r="Z11" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="AA11" s="18"/>
+      <c r="AA11" s="9"/>
       <c r="AK11" s="1"/>
       <c r="AL11" s="1"/>
       <c r="AM11" s="3"/>
@@ -1282,16 +1256,16 @@
       <c r="AS11" s="9"/>
     </row>
     <row r="12" spans="1:48" x14ac:dyDescent="0.2">
-      <c r="H12" s="14" t="s">
+      <c r="H12" t="s">
         <v>9</v>
       </c>
-      <c r="I12" s="14">
+      <c r="I12">
         <v>0.78745611026956841</v>
       </c>
-      <c r="Z12" s="14" t="s">
+      <c r="Z12" t="s">
         <v>8</v>
       </c>
-      <c r="AA12" s="14">
+      <c r="AA12">
         <v>1</v>
       </c>
       <c r="AK12" s="1"/>
@@ -1306,16 +1280,16 @@
       </c>
     </row>
     <row r="13" spans="1:48" x14ac:dyDescent="0.2">
-      <c r="H13" s="14" t="s">
+      <c r="H13" t="s">
         <v>10</v>
       </c>
-      <c r="I13" s="14">
+      <c r="I13">
         <v>0.57491222053913682</v>
       </c>
-      <c r="Z13" s="14" t="s">
+      <c r="Z13" t="s">
         <v>9</v>
       </c>
-      <c r="AA13" s="14">
+      <c r="AA13">
         <v>1</v>
       </c>
       <c r="AR13" t="s">
@@ -1326,16 +1300,16 @@
       </c>
     </row>
     <row r="14" spans="1:48" x14ac:dyDescent="0.2">
-      <c r="H14" s="14" t="s">
+      <c r="H14" t="s">
         <v>11</v>
       </c>
-      <c r="I14" s="14">
+      <c r="I14">
         <v>2.907390079813036E-2</v>
       </c>
-      <c r="Z14" s="14" t="s">
+      <c r="Z14" t="s">
         <v>10</v>
       </c>
-      <c r="AA14" s="14">
+      <c r="AA14">
         <v>65535</v>
       </c>
       <c r="AR14" t="s">
@@ -1346,16 +1320,16 @@
       </c>
     </row>
     <row r="15" spans="1:48" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="H15" s="15" t="s">
+      <c r="H15" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="I15" s="15">
+      <c r="I15" s="7">
         <v>9</v>
       </c>
-      <c r="Z15" s="14" t="s">
+      <c r="Z15" t="s">
         <v>11</v>
       </c>
-      <c r="AA15" s="14">
+      <c r="AA15">
         <v>0</v>
       </c>
       <c r="AR15" t="s">
@@ -1366,10 +1340,10 @@
       </c>
     </row>
     <row r="16" spans="1:48" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="Z16" s="15" t="s">
+      <c r="Z16" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="AA16" s="15">
+      <c r="AA16" s="7">
         <v>5</v>
       </c>
       <c r="AR16" s="7" t="s">
@@ -1385,20 +1359,20 @@
       </c>
     </row>
     <row r="18" spans="8:52" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="H18" s="16"/>
-      <c r="I18" s="16" t="s">
+      <c r="H18" s="8"/>
+      <c r="I18" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="J18" s="16" t="s">
+      <c r="J18" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="K18" s="16" t="s">
+      <c r="K18" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="L18" s="16" t="s">
+      <c r="L18" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="M18" s="16" t="s">
+      <c r="M18" s="8" t="s">
         <v>22</v>
       </c>
       <c r="Z18" t="s">
@@ -1409,38 +1383,38 @@
       </c>
     </row>
     <row r="19" spans="8:52" x14ac:dyDescent="0.2">
-      <c r="H19" s="14" t="s">
+      <c r="H19" t="s">
         <v>14</v>
       </c>
-      <c r="I19" s="14">
+      <c r="I19">
         <v>4</v>
       </c>
-      <c r="J19" s="14">
+      <c r="J19">
         <v>1.2526920834457455E-2</v>
       </c>
-      <c r="K19" s="14">
+      <c r="K19">
         <v>3.1317302086143637E-3</v>
       </c>
-      <c r="L19" s="14">
+      <c r="L19">
         <v>3.7049106011388777</v>
       </c>
       <c r="M19" s="5">
         <v>0.11632141510517437</v>
       </c>
-      <c r="Z19" s="16"/>
-      <c r="AA19" s="16" t="s">
+      <c r="Z19" s="8"/>
+      <c r="AA19" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="AB19" s="16" t="s">
+      <c r="AB19" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="AC19" s="16" t="s">
+      <c r="AC19" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="AD19" s="16" t="s">
+      <c r="AD19" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="AE19" s="16" t="s">
+      <c r="AE19" s="8" t="s">
         <v>22</v>
       </c>
       <c r="AR19" s="8"/>
@@ -1461,36 +1435,34 @@
       </c>
     </row>
     <row r="20" spans="8:52" x14ac:dyDescent="0.2">
-      <c r="H20" s="14" t="s">
+      <c r="H20" t="s">
         <v>15</v>
       </c>
-      <c r="I20" s="14">
+      <c r="I20">
         <v>4</v>
       </c>
-      <c r="J20" s="14">
+      <c r="J20">
         <v>3.3811668304781009E-3</v>
       </c>
-      <c r="K20" s="14">
+      <c r="K20">
         <v>8.4529170761952523E-4</v>
       </c>
-      <c r="L20" s="14"/>
-      <c r="M20" s="14"/>
-      <c r="Z20" s="14" t="s">
+      <c r="Z20" t="s">
         <v>14</v>
       </c>
-      <c r="AA20" s="14">
+      <c r="AA20">
         <v>4</v>
       </c>
-      <c r="AB20" s="14">
+      <c r="AB20">
         <v>4.4854456895200079E-4</v>
       </c>
-      <c r="AC20" s="14">
+      <c r="AC20">
         <v>1.121361422380002E-4</v>
       </c>
-      <c r="AD20" s="14" t="e">
+      <c r="AD20" t="e">
         <v>#NUM!</v>
       </c>
-      <c r="AE20" s="14" t="e">
+      <c r="AE20" t="e">
         <v>#NUM!</v>
       </c>
       <c r="AR20" t="s">
@@ -1513,32 +1485,30 @@
       </c>
     </row>
     <row r="21" spans="8:52" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="H21" s="15" t="s">
+      <c r="H21" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="I21" s="15">
+      <c r="I21" s="7">
         <v>8</v>
       </c>
-      <c r="J21" s="15">
+      <c r="J21" s="7">
         <v>1.5908087664935556E-2</v>
       </c>
-      <c r="K21" s="15"/>
-      <c r="L21" s="15"/>
-      <c r="M21" s="15"/>
-      <c r="Z21" s="14" t="s">
+      <c r="K21" s="7"/>
+      <c r="L21" s="7"/>
+      <c r="M21" s="7"/>
+      <c r="Z21" t="s">
         <v>15</v>
       </c>
-      <c r="AA21" s="14">
+      <c r="AA21">
         <v>0</v>
       </c>
-      <c r="AB21" s="14">
+      <c r="AB21">
         <v>0</v>
       </c>
-      <c r="AC21" s="14">
+      <c r="AC21">
         <v>65535</v>
       </c>
-      <c r="AD21" s="14"/>
-      <c r="AE21" s="14"/>
       <c r="AR21" t="s">
         <v>15</v>
       </c>
@@ -1553,18 +1523,18 @@
       </c>
     </row>
     <row r="22" spans="8:52" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="Z22" s="15" t="s">
+      <c r="Z22" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="AA22" s="15">
+      <c r="AA22" s="7">
         <v>4</v>
       </c>
-      <c r="AB22" s="15">
+      <c r="AB22" s="7">
         <v>4.4854456895200079E-4</v>
       </c>
-      <c r="AC22" s="15"/>
-      <c r="AD22" s="15"/>
-      <c r="AE22" s="15"/>
+      <c r="AC22" s="7"/>
+      <c r="AD22" s="7"/>
+      <c r="AE22" s="7"/>
       <c r="AR22" s="7" t="s">
         <v>16</v>
       </c>
@@ -1579,83 +1549,83 @@
       <c r="AW22" s="7"/>
     </row>
     <row r="23" spans="8:52" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="H23" s="16"/>
-      <c r="I23" s="16" t="s">
+      <c r="H23" s="8"/>
+      <c r="I23" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="J23" s="16" t="s">
+      <c r="J23" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="K23" s="16" t="s">
+      <c r="K23" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="L23" s="16" t="s">
+      <c r="L23" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="M23" s="16" t="s">
+      <c r="M23" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="N23" s="16" t="s">
+      <c r="N23" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="O23" s="16" t="s">
+      <c r="O23" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="P23" s="16" t="s">
+      <c r="P23" s="8" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="24" spans="8:52" x14ac:dyDescent="0.2">
-      <c r="H24" s="14" t="s">
+      <c r="H24" t="s">
         <v>17</v>
       </c>
-      <c r="I24" s="14">
+      <c r="I24">
         <v>8.8829814986594924E-2</v>
       </c>
-      <c r="J24" s="14">
+      <c r="J24">
         <v>0.11214301429564956</v>
       </c>
-      <c r="K24" s="14">
+      <c r="K24">
         <v>0.79211188984458181</v>
       </c>
       <c r="L24" s="5">
         <v>0.47262316611340538</v>
       </c>
-      <c r="M24" s="14">
+      <c r="M24">
         <v>-0.22252910813668747</v>
       </c>
-      <c r="N24" s="14">
+      <c r="N24">
         <v>0.40018873810987732</v>
       </c>
-      <c r="O24" s="14">
+      <c r="O24">
         <v>-0.22252910813668747</v>
       </c>
-      <c r="P24" s="14">
+      <c r="P24">
         <v>0.40018873810987732</v>
       </c>
-      <c r="Z24" s="16"/>
-      <c r="AA24" s="16" t="s">
+      <c r="Z24" s="8"/>
+      <c r="AA24" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="AB24" s="16" t="s">
+      <c r="AB24" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="AC24" s="16" t="s">
+      <c r="AC24" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="AD24" s="16" t="s">
+      <c r="AD24" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="AE24" s="16" t="s">
+      <c r="AE24" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="AF24" s="16" t="s">
+      <c r="AF24" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="AG24" s="16" t="s">
+      <c r="AG24" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="AH24" s="16" t="s">
+      <c r="AH24" s="8" t="s">
         <v>29</v>
       </c>
       <c r="AR24" s="8"/>
@@ -1685,58 +1655,58 @@
       </c>
     </row>
     <row r="25" spans="8:52" x14ac:dyDescent="0.2">
-      <c r="H25" s="14" t="s">
+      <c r="H25" t="s">
         <v>2</v>
       </c>
-      <c r="I25" s="14">
+      <c r="I25">
         <v>8.9295781641346873E-3</v>
       </c>
-      <c r="J25" s="14">
+      <c r="J25">
         <v>7.3201817031036927E-3</v>
       </c>
-      <c r="K25" s="14">
+      <c r="K25">
         <v>1.2198574470287566</v>
       </c>
       <c r="L25" s="5">
         <v>0.28952206412272408</v>
       </c>
-      <c r="M25" s="14">
+      <c r="M25">
         <v>-1.1394504494606007E-2</v>
       </c>
-      <c r="N25" s="14">
+      <c r="N25">
         <v>2.9253660822875383E-2</v>
       </c>
-      <c r="O25" s="14">
+      <c r="O25">
         <v>-1.1394504494606007E-2</v>
       </c>
-      <c r="P25" s="14">
+      <c r="P25">
         <v>2.9253660822875383E-2</v>
       </c>
-      <c r="Z25" s="14" t="s">
+      <c r="Z25" t="s">
         <v>17</v>
       </c>
-      <c r="AA25" s="14">
+      <c r="AA25">
         <v>-0.16398780754195261</v>
       </c>
-      <c r="AB25" s="14">
+      <c r="AB25">
         <v>0</v>
       </c>
-      <c r="AC25" s="14">
+      <c r="AC25">
         <v>65535</v>
       </c>
-      <c r="AD25" s="14" t="e">
+      <c r="AD25" t="e">
         <v>#NUM!</v>
       </c>
-      <c r="AE25" s="14" t="e">
+      <c r="AE25" t="e">
         <v>#VALUE!</v>
       </c>
-      <c r="AF25" s="14" t="e">
+      <c r="AF25" t="e">
         <v>#VALUE!</v>
       </c>
-      <c r="AG25" s="14">
+      <c r="AG25">
         <v>-0.16398780754195261</v>
       </c>
-      <c r="AH25" s="14">
+      <c r="AH25">
         <v>-0.16398780754195261</v>
       </c>
       <c r="AR25" t="s">
@@ -1768,58 +1738,58 @@
       </c>
     </row>
     <row r="26" spans="8:52" x14ac:dyDescent="0.2">
-      <c r="H26" s="14" t="s">
+      <c r="H26" t="s">
         <v>4</v>
       </c>
-      <c r="I26" s="14">
+      <c r="I26">
         <v>-5.045022529625437E-2</v>
       </c>
-      <c r="J26" s="14">
+      <c r="J26">
         <v>1.4743731183715332E-2</v>
       </c>
-      <c r="K26" s="14">
+      <c r="K26">
         <v>-3.4218085413804467</v>
       </c>
       <c r="L26" s="5">
         <v>2.673575409963317E-2</v>
       </c>
-      <c r="M26" s="14">
+      <c r="M26">
         <v>-9.1385385573632877E-2</v>
       </c>
-      <c r="N26" s="14">
+      <c r="N26">
         <v>-9.5150650188758658E-3</v>
       </c>
-      <c r="O26" s="14">
+      <c r="O26">
         <v>-9.1385385573632877E-2</v>
       </c>
-      <c r="P26" s="14">
+      <c r="P26">
         <v>-9.5150650188758658E-3</v>
       </c>
-      <c r="Z26" s="14" t="s">
+      <c r="Z26" t="s">
         <v>2</v>
       </c>
-      <c r="AA26" s="14">
+      <c r="AA26">
         <v>-2.5184424558947574E-3</v>
       </c>
-      <c r="AB26" s="14">
+      <c r="AB26">
         <v>0</v>
       </c>
-      <c r="AC26" s="14">
+      <c r="AC26">
         <v>65535</v>
       </c>
-      <c r="AD26" s="14" t="e">
+      <c r="AD26" t="e">
         <v>#NUM!</v>
       </c>
-      <c r="AE26" s="14">
+      <c r="AE26">
         <v>-2.5184424558947574E-3</v>
       </c>
-      <c r="AF26" s="14">
+      <c r="AF26">
         <v>-2.5184424558947574E-3</v>
       </c>
-      <c r="AG26" s="14">
+      <c r="AG26">
         <v>-2.5184424558947574E-3</v>
       </c>
-      <c r="AH26" s="14">
+      <c r="AH26">
         <v>-2.5184424558947574E-3</v>
       </c>
       <c r="AR26" t="s">
@@ -1851,58 +1821,58 @@
       </c>
     </row>
     <row r="27" spans="8:52" x14ac:dyDescent="0.2">
-      <c r="H27" s="14" t="s">
+      <c r="H27" t="s">
         <v>32</v>
       </c>
-      <c r="I27" s="14">
+      <c r="I27">
         <v>-8.0200410908007353E-3</v>
       </c>
-      <c r="J27" s="14">
+      <c r="J27">
         <v>7.2060343907267262E-3</v>
       </c>
-      <c r="K27" s="14">
+      <c r="K27">
         <v>-1.1129618117173483</v>
       </c>
       <c r="L27" s="5">
         <v>0.32809700347719589</v>
       </c>
-      <c r="M27" s="14">
+      <c r="M27">
         <v>-2.8027200002820919E-2</v>
       </c>
-      <c r="N27" s="14">
+      <c r="N27">
         <v>1.1987117821219447E-2</v>
       </c>
-      <c r="O27" s="14">
+      <c r="O27">
         <v>-2.8027200002820919E-2</v>
       </c>
-      <c r="P27" s="14">
+      <c r="P27">
         <v>1.1987117821219447E-2</v>
       </c>
-      <c r="Z27" s="14" t="s">
+      <c r="Z27" t="s">
         <v>32</v>
       </c>
-      <c r="AA27" s="14">
+      <c r="AA27">
         <v>-7.9117670552468107E-3</v>
       </c>
-      <c r="AB27" s="14">
+      <c r="AB27">
         <v>0</v>
       </c>
-      <c r="AC27" s="14">
+      <c r="AC27">
         <v>65535</v>
       </c>
-      <c r="AD27" s="14" t="e">
+      <c r="AD27" t="e">
         <v>#NUM!</v>
       </c>
-      <c r="AE27" s="14">
+      <c r="AE27">
         <v>-7.9117670552468107E-3</v>
       </c>
-      <c r="AF27" s="14">
+      <c r="AF27">
         <v>-7.9117670552468107E-3</v>
       </c>
-      <c r="AG27" s="14">
+      <c r="AG27">
         <v>-7.9117670552468107E-3</v>
       </c>
-      <c r="AH27" s="14">
+      <c r="AH27">
         <v>-7.9117670552468107E-3</v>
       </c>
       <c r="AR27" t="s">
@@ -1934,58 +1904,58 @@
       </c>
     </row>
     <row r="28" spans="8:52" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="H28" s="15" t="s">
+      <c r="H28" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="I28" s="15">
+      <c r="I28" s="7">
         <v>-9.753810165585115E-3</v>
       </c>
-      <c r="J28" s="15">
+      <c r="J28" s="7">
         <v>1.0277344278089325E-2</v>
       </c>
-      <c r="K28" s="15">
+      <c r="K28" s="7">
         <v>-0.94905939721992649</v>
       </c>
       <c r="L28" s="4">
         <v>0.39633165511937318</v>
       </c>
-      <c r="M28" s="15">
+      <c r="M28" s="7">
         <v>-3.828829238091877E-2</v>
       </c>
-      <c r="N28" s="15">
+      <c r="N28" s="7">
         <v>1.878067204974854E-2</v>
       </c>
-      <c r="O28" s="15">
+      <c r="O28" s="7">
         <v>-3.828829238091877E-2</v>
       </c>
-      <c r="P28" s="15">
+      <c r="P28" s="7">
         <v>1.878067204974854E-2</v>
       </c>
-      <c r="Z28" s="14" t="s">
+      <c r="Z28" t="s">
         <v>33</v>
       </c>
-      <c r="AA28" s="14">
+      <c r="AA28">
         <v>2.9666351265587171E-3</v>
       </c>
-      <c r="AB28" s="14">
+      <c r="AB28">
         <v>0</v>
       </c>
-      <c r="AC28" s="14">
+      <c r="AC28">
         <v>65535</v>
       </c>
-      <c r="AD28" s="14" t="e">
+      <c r="AD28" t="e">
         <v>#NUM!</v>
       </c>
-      <c r="AE28" s="14">
+      <c r="AE28">
         <v>2.9666351265587171E-3</v>
       </c>
-      <c r="AF28" s="14">
+      <c r="AF28">
         <v>2.9666351265587171E-3</v>
       </c>
-      <c r="AG28" s="14">
+      <c r="AG28">
         <v>2.9666351265587171E-3</v>
       </c>
-      <c r="AH28" s="14">
+      <c r="AH28">
         <v>2.9666351265587171E-3</v>
       </c>
       <c r="AR28" t="s">
@@ -2017,31 +1987,31 @@
       </c>
     </row>
     <row r="29" spans="8:52" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="Z29" s="15" t="s">
+      <c r="Z29" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="AA29" s="15">
+      <c r="AA29" s="7">
         <v>-8.0746127751403366E-4</v>
       </c>
-      <c r="AB29" s="15">
+      <c r="AB29" s="7">
         <v>0</v>
       </c>
-      <c r="AC29" s="15">
+      <c r="AC29" s="7">
         <v>65535</v>
       </c>
-      <c r="AD29" s="15" t="e">
+      <c r="AD29" s="7" t="e">
         <v>#NUM!</v>
       </c>
-      <c r="AE29" s="15">
+      <c r="AE29" s="7">
         <v>-8.0746127751403366E-4</v>
       </c>
-      <c r="AF29" s="15">
+      <c r="AF29" s="7">
         <v>-8.0746127751403366E-4</v>
       </c>
-      <c r="AG29" s="15">
+      <c r="AG29" s="7">
         <v>-8.0746127751403366E-4</v>
       </c>
-      <c r="AH29" s="15">
+      <c r="AH29" s="7">
         <v>-8.0746127751403366E-4</v>
       </c>
       <c r="AR29" s="7" t="s">
